--- a/etf_holdings/2026-10-27_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-27_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-27 00:06:56</t>
+          <t>2026-10-27 22:41:25</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,33 +509,33 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-1.45%2385</t>
+          <t>+0.63%2400</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-1.45%</t>
+          <t>+0.63%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2385</v>
+        <v>2400</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>11.34%12,671,000</t>
+          <t>11.75%13,046,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>11.34%</t>
+          <t>11.75%</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>12671000</v>
+        <v>13046000</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-27 00:06:56</t>
+          <t>2026-10-27 22:41:25</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -565,38 +565,38 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2383台光電</t>
+          <t>3037欣興</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+1.6%5070</t>
+          <t>-2.3%1060</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+1.6%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5070</v>
+        <v>1060</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8.23%4,328,000</t>
+          <t>7.83%19,689,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>8.23%</t>
+          <t>7.83%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>4328000</v>
+        <v>19689000</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-27 00:06:56</t>
+          <t>2026-10-27 22:41:25</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -626,38 +626,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3037欣興</t>
+          <t>2454聯發科</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-1.36%1085</t>
+          <t>-1.25%3960</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-1.36%</t>
+          <t>-1.25%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1085</v>
+        <v>3960</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8.01%19,689,000</t>
+          <t>7.78%5,233,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>8.01%</t>
+          <t>7.78%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>19689000</v>
+        <v>5233000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:06:56</t>
+          <t>2026-10-27 22:41:25</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -687,38 +687,38 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2454聯發科</t>
+          <t>2383台光電</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-3.14%4010</t>
+          <t>-6.31%4750</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-3.14%</t>
+          <t>-6.31%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>4010</v>
+        <v>4750</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>7.74%5,143,000</t>
+          <t>7.72%4,328,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>7.74%</t>
+          <t>7.72%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>5143000</v>
+        <v>4328000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>-0.51%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-27 00:06:56</t>
+          <t>2026-10-27 22:41:25</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,33 +753,33 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-2.78%3145</t>
+          <t>-0.48%3130</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-2.78%</t>
+          <t>-0.48%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>3145</v>
+        <v>3130</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>7.62%6,457,000</t>
+          <t>7.68%6,537,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>7.62%</t>
+          <t>7.68%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>6457000</v>
+        <v>6537000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-27 00:06:56</t>
+          <t>2026-10-27 22:41:25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-7.12%6070</t>
+          <t>-3.46%5860</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-7.12%</t>
+          <t>-3.46%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>6070</v>
+        <v>5860</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5.72%2,512,000</t>
+          <t>5.52%2,512,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.72%</t>
+          <t>5.52%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-27 00:06:56</t>
+          <t>2026-10-27 22:41:25</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>6223旺矽</t>
+          <t>2327國巨*</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-2.3%4890</t>
+          <t>+2.76%521</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>+2.76%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>4890</v>
+        <v>521</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4.59%2,504,000</t>
+          <t>4.60%23,519,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4.59%</t>
+          <t>4.60%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>2504000</v>
+        <v>23519000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-27 00:06:56</t>
+          <t>2026-10-27 22:41:25</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2327國巨*</t>
+          <t>6223旺矽</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-6.46%507</t>
+          <t>-2.04%4790</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-6.46%</t>
+          <t>-2.04%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>507</v>
+        <v>4790</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.47%23,519,000</t>
+          <t>4.50%2,504,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.47%</t>
+          <t>4.50%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>23519000</v>
+        <v>2504000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.30%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-27 00:06:56</t>
+          <t>2026-10-27 22:41:25</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-4%1560</t>
+          <t>-3.21%1510</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-3.21%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1560</v>
+        <v>1510</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.44%7,582,000</t>
+          <t>4.30%7,582,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.44%</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-27 00:06:56</t>
+          <t>2026-10-27 22:41:25</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,25 +1058,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-5.6%1265</t>
+          <t>-0.79%1255</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1265</v>
+        <v>1255</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.24%8,937,000</t>
+          <t>4.21%8,937,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.24%</t>
+          <t>4.21%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.25%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-27 00:06:56</t>
+          <t>2026-10-27 22:41:25</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,25 +1119,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-2.2%1775</t>
+          <t>-0.85%1760</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-0.85%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1775</v>
+        <v>1760</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4.22%6,331,000</t>
+          <t>4.18%6,331,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4.22%</t>
+          <t>4.18%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-27 00:06:56</t>
+          <t>2026-10-27 22:41:25</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>2303聯電</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-5.33%1420</t>
+          <t>-2.39%122.5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-5.33%</t>
+          <t>-2.39%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1420</v>
+        <v>122.5</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.85%7,224,000</t>
+          <t>3.66%79,618,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.85%</t>
+          <t>3.66%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>7224000</v>
+        <v>79618000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-27 00:06:56</t>
+          <t>2026-10-27 22:41:25</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2303聯電</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-1.95%125.5</t>
+          <t>-9.86%1280</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-1.95%</t>
+          <t>-9.86%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>125.5</v>
+        <v>1280</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.75%79,618,000</t>
+          <t>3.47%7,224,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.75%</t>
+          <t>3.47%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>79618000</v>
+        <v>7224000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.37%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-27 00:06:56</t>
+          <t>2026-10-27 22:41:25</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,33 +1302,33 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-6.69%1115</t>
+          <t>-3.14%1080</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-6.69%</t>
+          <t>-3.14%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1115</v>
+        <v>1080</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.89%6,899,000</t>
+          <t>2.83%6,979,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.89%</t>
+          <t>2.83%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>6899000</v>
+        <v>6979000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.20%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-27 00:06:56</t>
+          <t>2026-10-27 22:41:25</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3443創意</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-5.19%7585</t>
+          <t>-0.46%651</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-5.19%</t>
+          <t>-0.46%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>7585</v>
+        <v>651</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.42%852,000</t>
+          <t>2.44%9,968,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.42%</t>
+          <t>2.44%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>852000</v>
+        <v>9968000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-27 00:06:57</t>
+          <t>2026-10-27 22:41:29</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,27 +1424,27 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-2.13%1840</t>
+          <t>+5.98%1950</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-2.13%</t>
+          <t>+5.98%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1840</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.27%3,281,561</t>
+          <t>2.40%3,281,561</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.27%</t>
+          <t>2.40%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-27 00:06:57</t>
+          <t>2026-10-27 22:41:29</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1482,40 +1482,40 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3711日月光投控</t>
+          <t>3443創意</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-4.39%654</t>
+          <t>-2.04%7430</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-4.39%</t>
+          <t>-2.04%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>7430</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.18%8,895,000</t>
+          <t>2.38%852,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.18%</t>
+          <t>2.38%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>8895000</v>
+        <v>852000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-27 00:06:57</t>
+          <t>2026-10-27 22:41:29</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1550,27 +1550,27 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-3.85%1875</t>
+          <t>-7.47%1735</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-3.85%</t>
+          <t>-7.47%</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1875</t>
+          <t>1735</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.03%2,887,848</t>
+          <t>1.88%2,887,848</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>1.88%</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-27 00:06:57</t>
+          <t>2026-10-27 22:41:29</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1613,17 +1613,17 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-3.06%16010</t>
+          <t>+0.03%16015</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-3.06%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>16010</t>
+          <t>16015</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-27 00:06:57</t>
+          <t>2026-10-27 22:41:29</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1676,35 +1676,35 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-2.51%2335</t>
+          <t>-3.64%2250</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-2.51%</t>
+          <t>-3.64%</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2335</t>
+          <t>2250</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.81%919,000</t>
+          <t>0.82%969,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.82%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>919000</v>
+        <v>969000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-27 00:06:57</t>
+          <t>2026-10-27 22:41:29</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1739,35 +1739,35 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-5.58%262.5</t>
+          <t>+2.48%269</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-5.58%</t>
+          <t>+2.48%</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>262.5</t>
+          <t>269</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.65%6,587,450</t>
+          <t>0.76%7,556,450</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.65%</t>
+          <t>0.76%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>6587450</v>
+        <v>7556450</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-27 00:06:57</t>
+          <t>2026-10-27 22:41:29</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1802,27 +1802,27 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-6.02%1560</t>
+          <t>-6.09%1465</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-6.02%</t>
+          <t>-6.09%</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>1465</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.57%981,000</t>
+          <t>0.54%981,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-27 00:06:57</t>
+          <t>2026-10-27 22:41:29</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1865,27 +1865,27 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-5.11%3065</t>
+          <t>-5.06%2910</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-5.11%</t>
+          <t>-5.06%</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>3065</t>
+          <t>2910</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.54%470,000</t>
+          <t>0.51%470,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.51%</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-27 00:06:57</t>
+          <t>2026-10-27 22:41:29</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1928,17 +1928,17 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-6.98%246.5</t>
+          <t>+0.61%248</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-6.98%</t>
+          <t>+0.61%</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>248</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-27 00:06:57</t>
+          <t>2026-10-27 22:41:29</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1991,17 +1991,17 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-2.56%190</t>
+          <t>+0.26%190.5</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-2.56%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>190.5</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-27 00:06:57</t>
+          <t>2026-10-27 22:41:29</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2054,27 +2054,27 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-7.33%215</t>
+          <t>-3.49%207.5</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-7.33%</t>
+          <t>-3.49%</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>207.5</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.18%2,185,000</t>
+          <t>0.17%2,185,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.18%</t>
+          <t>0.17%</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-27 00:06:57</t>
+          <t>2026-10-27 22:41:29</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2112,27 +2112,27 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>6515穎崴</t>
+          <t>4979華星光</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-3.52%4795</t>
+          <t>+3.89%467.5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-3.52%</t>
+          <t>+3.89%</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>4795</t>
+          <t>467.5</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.17%93,000</t>
+          <t>0.17%957,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2141,11 +2141,11 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>93000</v>
+        <v>957000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-27 00:06:57</t>
+          <t>2026-10-27 22:41:29</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2175,40 +2175,40 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>4979華星光</t>
+          <t>6515穎崴</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-7.79%450</t>
+          <t>-0.42%4775</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-7.79%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>4775</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.16%957,000</t>
+          <t>0.15%85,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.16%</t>
+          <t>0.15%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>957000</v>
+        <v>85000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-27 00:06:57</t>
+          <t>2026-10-27 22:41:29</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2238,40 +2238,40 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>8210勤誠</t>
+          <t>6191精成科</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-4.74%764</t>
+          <t>-2.34%87.7</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-4.74%</t>
+          <t>-2.34%</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.14%478,000</t>
+          <t>0.13%3,921,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.14%</t>
+          <t>0.13%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>478000</v>
+        <v>3921000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-27 00:06:58</t>
+          <t>2026-10-27 22:41:31</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2301,38 +2301,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>6191精成科</t>
+          <t>8210勤誠</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-2.6%89.8</t>
+          <t>+1.44%775</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>+1.44%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>89.8</v>
+        <v>775</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.13%3,921,000</t>
+          <t>0.11%378,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.13%</t>
+          <t>0.11%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>3921000</v>
+        <v>378000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-27 00:06:58</t>
+          <t>2026-10-27 22:41:31</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2367,25 +2367,25 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-9.02%438.5</t>
+          <t>-4.1%420.5</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-9.02%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>438.5</v>
+        <v>420.5</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.11%654,000</t>
+          <t>0.10%654,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>0.10%</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-27 00:06:58</t>
+          <t>2026-10-27 22:41:31</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2428,25 +2428,25 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-5.48%172.5</t>
+          <t>-8.7%157.5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-5.48%</t>
+          <t>-8.7%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>172.5</v>
+        <v>157.5</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.11%1,740,000</t>
+          <t>0.10%1,740,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>0.10%</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-27 00:06:58</t>
+          <t>2026-10-27 22:41:31</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2489,16 +2489,16 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-5.26%1260</t>
+          <t>+1.98%1285</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-5.26%</t>
+          <t>+1.98%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1260</v>
+        <v>1285</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-27 00:06:58</t>
+          <t>2026-10-27 22:41:31</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2550,16 +2550,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-0.26%19.55</t>
+          <t>+1.02%19.75</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>+1.02%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>19.55</v>
+        <v>19.75</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-27 00:06:58</t>
+          <t>2026-10-27 22:41:31</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2611,16 +2611,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-6.65%224.5</t>
+          <t>-3.79%216</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-6.65%</t>
+          <t>-3.79%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>224.5</v>
+        <v>216</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-27 00:06:58</t>
+          <t>2026-10-27 22:41:31</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2672,16 +2672,16 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-8.21%290.5</t>
+          <t>-4.13%278.5</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-8.21%</t>
+          <t>-4.13%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>290.5</v>
+        <v>278.5</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-27 00:06:58</t>
+          <t>2026-10-27 22:41:31</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-5.8%3495</t>
+          <t>0%3495</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-27 00:06:58</t>
+          <t>2026-10-27 22:41:31</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2794,16 +2794,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-2.7%79.4</t>
+          <t>-0.5%79</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>79.40000000000001</v>
+        <v>79</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-27 00:06:58</t>
+          <t>2026-10-27 22:41:31</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2855,16 +2855,16 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-1.79%1100</t>
+          <t>+3.64%1140</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-1.79%</t>
+          <t>+3.64%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1100</v>
+        <v>1140</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-27 00:06:58</t>
+          <t>2026-10-27 22:41:31</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2916,16 +2916,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+0.08%6175</t>
+          <t>-2.83%6000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-2.83%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>6175</v>
+        <v>6000</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-27 00:06:58</t>
+          <t>2026-10-27 22:41:31</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2977,16 +2977,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-1.9%567</t>
+          <t>-8.29%520</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-1.9%</t>
+          <t>-8.29%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>567</v>
+        <v>520</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-27 00:06:58</t>
+          <t>2026-10-27 22:41:31</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3038,16 +3038,16 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-1.98%322</t>
+          <t>+1.71%327.5</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-1.98%</t>
+          <t>+1.71%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>322</v>
+        <v>327.5</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-27 00:06:58</t>
+          <t>2026-10-27 22:41:31</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3099,16 +3099,16 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-5.15%414</t>
+          <t>+6.52%441</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-5.15%</t>
+          <t>+6.52%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>414</v>
+        <v>441</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-27 00:06:58</t>
+          <t>2026-10-27 22:41:31</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:00</t>
+          <t>2026-10-27 22:41:32</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3221,16 +3221,16 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-1.49%1980</t>
+          <t>-1.26%1955</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-1.49%</t>
+          <t>-1.26%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>1980</v>
+        <v>1955</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:00</t>
+          <t>2026-10-27 22:41:32</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3282,16 +3282,16 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-6.14%826</t>
+          <t>-1.45%814</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-6.14%</t>
+          <t>-1.45%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>826</v>
+        <v>814</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:00</t>
+          <t>2026-10-27 22:41:32</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3343,16 +3343,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-6.44%95.9</t>
+          <t>+1.15%97</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-6.44%</t>
+          <t>+1.15%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>95.90000000000001</v>
+        <v>97</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:00</t>
+          <t>2026-10-27 22:41:32</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3404,16 +3404,16 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-2%245</t>
+          <t>+1.02%247.5</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>+1.02%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>245</v>
+        <v>247.5</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:00</t>
+          <t>2026-10-27 22:41:32</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3465,16 +3465,16 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-3.3%161</t>
+          <t>+0.31%161.5</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>+0.31%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>161</v>
+        <v>161.5</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:00</t>
+          <t>2026-10-27 22:41:32</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3526,16 +3526,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-3.46%153.5</t>
+          <t>-2.28%150</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-3.46%</t>
+          <t>-2.28%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>153.5</v>
+        <v>150</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>

--- a/etf_holdings/2026-10-27_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-27_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:25</t>
+          <t>2026-10-27 22:54:11</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:25</t>
+          <t>2026-10-27 22:54:11</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:25</t>
+          <t>2026-10-27 22:54:11</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:25</t>
+          <t>2026-10-27 22:54:11</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:25</t>
+          <t>2026-10-27 22:54:11</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:25</t>
+          <t>2026-10-27 22:54:11</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:25</t>
+          <t>2026-10-27 22:54:11</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:25</t>
+          <t>2026-10-27 22:54:11</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:25</t>
+          <t>2026-10-27 22:54:11</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:25</t>
+          <t>2026-10-27 22:54:11</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:25</t>
+          <t>2026-10-27 22:54:11</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:25</t>
+          <t>2026-10-27 22:54:11</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:25</t>
+          <t>2026-10-27 22:54:11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:25</t>
+          <t>2026-10-27 22:54:11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:25</t>
+          <t>2026-10-27 22:54:11</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:29</t>
+          <t>2026-10-27 22:54:12</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:29</t>
+          <t>2026-10-27 22:54:12</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:29</t>
+          <t>2026-10-27 22:54:12</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:29</t>
+          <t>2026-10-27 22:54:12</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:29</t>
+          <t>2026-10-27 22:54:12</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:29</t>
+          <t>2026-10-27 22:54:12</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:29</t>
+          <t>2026-10-27 22:54:12</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:29</t>
+          <t>2026-10-27 22:54:12</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:29</t>
+          <t>2026-10-27 22:54:12</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:29</t>
+          <t>2026-10-27 22:54:12</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:29</t>
+          <t>2026-10-27 22:54:12</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:29</t>
+          <t>2026-10-27 22:54:12</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:29</t>
+          <t>2026-10-27 22:54:12</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:29</t>
+          <t>2026-10-27 22:54:12</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:31</t>
+          <t>2026-10-27 22:54:14</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:31</t>
+          <t>2026-10-27 22:54:14</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:31</t>
+          <t>2026-10-27 22:54:14</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:31</t>
+          <t>2026-10-27 22:54:14</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:31</t>
+          <t>2026-10-27 22:54:14</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:31</t>
+          <t>2026-10-27 22:54:14</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:31</t>
+          <t>2026-10-27 22:54:14</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:31</t>
+          <t>2026-10-27 22:54:14</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:31</t>
+          <t>2026-10-27 22:54:14</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:31</t>
+          <t>2026-10-27 22:54:14</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:31</t>
+          <t>2026-10-27 22:54:14</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:31</t>
+          <t>2026-10-27 22:54:14</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:31</t>
+          <t>2026-10-27 22:54:14</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:31</t>
+          <t>2026-10-27 22:54:14</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:31</t>
+          <t>2026-10-27 22:54:14</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:32</t>
+          <t>2026-10-27 22:54:15</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:32</t>
+          <t>2026-10-27 22:54:15</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:32</t>
+          <t>2026-10-27 22:54:15</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:32</t>
+          <t>2026-10-27 22:54:15</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:32</t>
+          <t>2026-10-27 22:54:15</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:32</t>
+          <t>2026-10-27 22:54:15</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
